--- a/docs/DD_北海道3町_20261016/PX案件チェックシート_松前町札前・館浜.xlsx
+++ b/docs/DD_北海道3町_20261016/PX案件チェックシート_松前町札前・館浜.xlsx
@@ -582,7 +582,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>作成日：2026-10-16</t>
+          <t>作成日：2026-10-19</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="E7" s="15" t="inlineStr">
         <is>
-          <t>一部該当：No.8 札前372-2が急傾斜地の崩壊 特別警戒区域に接触</t>
+          <t>一部該当：No.8 札前372-2の端（約0.3%）が急傾斜地の崩壊 警戒区域・特別警戒区域（松前札前4、2020/12/11指定）にかかる</t>
         </is>
       </c>
       <c r="F7" s="16" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>重ねるハザードマップで「土砂災害（特別）警戒区域」をON。 / 他15筆は土砂災害警戒区域・危険箇所とも着色なし</t>
+          <t>重ねるハザードマップで「土砂災害（特別）警戒区域」をON。 / 不動産情報ライブラリ・地理院タイルで確認。他15筆は該当なし。配置で回避可能か要確認</t>
         </is>
       </c>
       <c r="H7" s="9" t="inlineStr">
@@ -1045,9 +1045,9 @@
           <t>6. 液状化危険度</t>
         </is>
       </c>
-      <c r="E8" s="17" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>一部 液状化しやすい：No.9 札前372-15・No.11 372-26（三角州・海岸低地）</t>
         </is>
       </c>
       <c r="F8" s="16" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>J-SHIS表層地盤＋各都道府県の液状化マップで確認。</t>
+          <t>J-SHIS表層地盤＋各都道府県の液状化マップで確認。 / 他14筆は液状化しにくい（砂礫質台地）。不動産情報ライブラリ（地形区分に基づく液状化の発生傾向）</t>
         </is>
       </c>
       <c r="H8" s="9" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>自治体の都市計画情報(web GIS)で区域区分を確認。 / 国土数値情報 都市地域(2018)に当町の都市計画区域の指定なし</t>
+          <t>自治体の都市計画情報(web GIS)で区域区分を確認。 / 国土数値情報 都市地域(2018)に当町の都市計画区域の指定なし／不動産情報ライブラリでも区域区分・用途地域なし</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>地点はGoogleマップ航空写真（座標）で確認。農地区分はeMAFF農地ナビ（住所/地番検索）、種別(1/2/3種)は農業委員会へ照会。 / 館浜4筆(No.1〜4)は農業地域内・農用地区域外。農用地区域なら農振除外が必要（除外は年1〜2回・半年〜1年）（出典：法務省地図XML(G空間 2026)の筆ポリゴン×国土数値情報 土地利用基本計画(2015)／地理院ハザードタイル。1/2.5万〜5万精度のため境界付近は要確認）</t>
+          <t>地点はGoogleマップ航空写真（座標）で確認。農地区分はeMAFF農地ナビ（住所/地番検索）、種別(1/2/3種)は農業委員会へ照会。 / 館浜4筆(No.1〜4)は農業地域内・農用地区域外。農用地区域なら農振除外が必要（除外は年1〜2回・半年〜1年）（出典：不動産情報ライブラリ(2026-10-19取得)／法務省地図XML(G空間 2026)の筆ポリゴン×国土数値情報 土地利用基本計画(2015)／地理院ハザードタイル。1/2.5万〜5万精度のため境界付近は要確認）</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>自然公園・都市公園の区域内かを確認。 / No.8 14m／No.11 27m／No.7 34m。境界精度上、区域内の可能性あり→道・振興局に区域図照会（出典：法務省地図XML(G空間 2026)の筆ポリゴン×国土数値情報 土地利用基本計画(2015)／地理院ハザードタイル。1/2.5万〜5万精度のため境界付近は要確認）</t>
+          <t>自然公園・都市公園の区域内かを確認。 / No.8 14m／No.11 27m／No.7 34m。境界精度上、区域内の可能性あり→道・振興局に区域図照会（出典：不動産情報ライブラリ(2026-10-19取得)／法務省地図XML(G空間 2026)の筆ポリゴン×国土数値情報 土地利用基本計画(2015)／地理院ハザードタイル。1/2.5万〜5万精度のため境界付近は要確認）</t>
         </is>
       </c>
       <c r="H15" s="9" t="inlineStr">
@@ -2061,7 +2061,7 @@
       <c r="O17" s="24" t="inlineStr"/>
       <c r="P17" s="24" t="inlineStr">
         <is>
-          <t>No.8 札前372-2が急傾斜 特別警戒区域に接触（地理院タイル）</t>
+          <t>No.8 札前372-2の端が急傾斜 特別警戒区域（松前札前4）にかかる。区域外に配置すれば対象外</t>
         </is>
       </c>
     </row>
